--- a/insights/20251230-20241230-insights/Anchor_Revenue.xlsx
+++ b/insights/20251230-20241230-insights/Anchor_Revenue.xlsx
@@ -49,10 +49,10 @@
     <t>account</t>
   </si>
   <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
   </si>
   <si>
     <t>department</t>
@@ -481,7 +481,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2">
-        <v>8407.3300</v>
+        <v>202735.7800</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -495,7 +495,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>202735.7800</v>
+        <v>8407.3300</v>
       </c>
     </row>
     <row r="4" spans="1:4">
